--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Bivariado/correlacion_spearman.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Bivariado/correlacion_spearman.xlsx
@@ -642,35 +642,37 @@
         <v>0.05049170319524004</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09450227822415139</v>
+        <v>0.07730735324146684</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06844400528290401</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-0.173639409392216</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.02757852901484674</v>
+      </c>
       <c r="O2" t="n">
-        <v>0.06440917038609663</v>
+        <v>-0.02757852901484674</v>
       </c>
       <c r="P2" t="n">
         <v>0.03900831531619792</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.03153571635729599</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.02165989122105998</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.0793980649914357</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.03069077471302442</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.03214645210433645</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06440917038609663</v>
+        <v>-0.1456855212497464</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
@@ -750,35 +752,37 @@
         <v>0.02191633582910032</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.08276826150638558</v>
+        <v>-0.02266869897885533</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07702390378756885</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>0.2671792033141727</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8542507163576309</v>
+      </c>
       <c r="O3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.8542507163576309</v>
       </c>
       <c r="P3" t="n">
         <v>0.2522089352340383</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.6910184067105104</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.5353784650110955</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.5391310127459359</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.794300946050853</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.1859161716969164</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1101944348386703</v>
+        <v>-0.2977193605035862</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
@@ -858,35 +862,37 @@
         <v>0.02570805936791152</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03538218822904182</v>
+        <v>-0.02120833173508577</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01942886514936889</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>-0.01982727127983493</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7571819249846923</v>
+      </c>
       <c r="O4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.7571819249846923</v>
       </c>
       <c r="P4" t="n">
         <v>0.2353950062184357</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.7382166498895558</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.6993819380518612</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.590548807253591</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.826454738200026</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.09782688783609415</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.03682187877349084</v>
+        <v>-0.4526026019591243</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
@@ -966,35 +972,37 @@
         <v>0.05722921123487956</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0273122243061387</v>
+        <v>-0.01818195339100029</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03038602528837508</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>0.1673835022509428</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8726278050195725</v>
+      </c>
       <c r="O5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.8726278050195725</v>
       </c>
       <c r="P5" t="n">
         <v>0.2912330591027843</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.75782853486202</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.6134903817115854</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.611796914141652</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.8563239866598242</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.1768107388140629</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.08724386798967174</v>
+        <v>-0.4128148165287109</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
@@ -1074,35 +1082,37 @@
         <v>0.02161236928613862</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1843288590634454</v>
+        <v>0.07068881556467677</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1671010233627738</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>-0.4267131525990377</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.4580190361126076</v>
+      </c>
       <c r="O6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.4580190361126076</v>
       </c>
       <c r="P6" t="n">
         <v>-0.01614093379617234</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.2305649712811109</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.09114528105726209</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.08472991209930328</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.2813198375645091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.1336565579070708</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.1367417610658745</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
@@ -1182,35 +1192,37 @@
         <v>0.1641058074027298</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0460886543068027</v>
+        <v>0.03381951937622345</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05606836865316756</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>0.05752565152876836</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.005561860264077447</v>
+      </c>
       <c r="O7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>0.005561860264077447</v>
       </c>
       <c r="P7" t="n">
         <v>0.447420545960082</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>0.04984873366356304</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.1270453105501432</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>0.1640220113992529</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.0255063758095474</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.02746666031656214</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.2058113265765833</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
@@ -1290,35 +1302,37 @@
         <v>-0.00893514196721569</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1139246677120228</v>
+        <v>0.1470775409802016</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08067647901768621</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>0.03520391997587036</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2506287708513495</v>
+      </c>
       <c r="O8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.2506287708513495</v>
       </c>
       <c r="P8" t="n">
         <v>-0.186303389833267</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.1503606267718496</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.2054597298378407</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.08108973939169131</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.2671924482255924</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.1003925880219537</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.03047374490297631</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
@@ -1398,33 +1412,35 @@
         <v>-0.2545764913553429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4767312946227962</v>
+        <v>0.5891746791302561</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>0.1303351507972746</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1860083510656061</v>
+      </c>
       <c r="O9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.1860083510656061</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>-0.07966649663613579</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>-0.2167348679785508</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.223606797749979</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.1256561724875087</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.6623703042426295</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5976143046671968</v>
+        <v>-0.3115374735156035</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
@@ -1504,12 +1520,14 @@
         <v>-0.1494618957003883</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04367131467411467</v>
+        <v>0.2049507033286523</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1612,35 +1630,37 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1057481450515653</v>
+        <v>0.1579530902994056</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1248361629009714</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>-0.0283054096970937</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.01101381771178504</v>
+      </c>
       <c r="O11" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.01101381771178504</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.03760109012815547</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.1257372123861838</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2182318387368158</v>
+        <v>0.04594375584248041</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2182318387368158</v>
+        <v>0.02581816191170443</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2182318387368158</v>
+        <v>0.01647412365930556</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.05321488691929668</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
@@ -1690,78 +1710,108 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09450227822415139</v>
+        <v>0.07730735324146684</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.08276826150638558</v>
+        <v>-0.02266869897885533</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03538218822904182</v>
+        <v>-0.02120833173508577</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0273122243061387</v>
+        <v>-0.01818195339100029</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1843288590634454</v>
+        <v>0.07068881556467677</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0460886543068027</v>
+        <v>0.03381951937622345</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1139246677120228</v>
+        <v>0.1470775409802016</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4767312946227962</v>
+        <v>0.5891746791302561</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04367131467411467</v>
+        <v>0.2049507033286523</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1057481450515653</v>
+        <v>0.1579530902994056</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9534625892455924</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>-0.1108808467440229</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1481053181946476</v>
+      </c>
       <c r="O12" t="n">
-        <v>0.2279211529192759</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>0.1481053181946476</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
-        <v>0.2279211529192759</v>
+        <v>-0.07780025828151069</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2279211529192759</v>
+        <v>-0.3312642154769886</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.2090602720231013</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.1091781663217261</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.595077465684646</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2279211529192759</v>
+        <v>-0.2696564558138487</v>
       </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.09194621406122841</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.1360120905009796</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.08143720110537678</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.2600731374244867</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.1847397329184985</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.008032162300804285</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.07980272769832711</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1584649790632748</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.08192901177024151</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.165142301603474</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.008859623899229174</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.2960616827146957</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1770,78 +1820,108 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06844400528290401</v>
+        <v>-0.173639409392216</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.07702390378756885</v>
+        <v>0.2671792033141727</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01942886514936889</v>
+        <v>-0.01982727127983493</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03038602528837508</v>
+        <v>0.1673835022509428</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1671010233627738</v>
+        <v>-0.4267131525990377</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05606836865316756</v>
+        <v>0.05752565152876836</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.08067647901768621</v>
+        <v>0.03520391997587036</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.1303351507972746</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1248361629009714</v>
+        <v>-0.0283054096970937</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9534625892455924</v>
+        <v>-0.1108808467440229</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0.3099265673991937</v>
+      </c>
       <c r="O13" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+        <v>0.3099265673991937</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7378647873726218</v>
+      </c>
       <c r="Q13" t="n">
-        <v>0.2390457218668787</v>
+        <v>-0.1298852140589887</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2390457218668787</v>
+        <v>-0.2724606851434096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2390457218668787</v>
+        <v>-0.1115068113893674</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2390457218668787</v>
+        <v>0.1646049004000574</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2390457218668787</v>
+        <v>0.3385714808706034</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2390457218668787</v>
+        <v>0.2740219131903385</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.5030030300035687</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.0490880693673816</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.3059252255649718</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.4306884410120977</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.1975926700229838</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.504510918892574</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.3311701420320236</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.4970370832912829</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2747742542411711</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.008082177995465454</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.003704420553899844</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.237519506159561</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.3600966517658488</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1849,41 +1929,109 @@
           <t>POBLACION TOTAL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>-0.02757852901484674</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8542507163576309</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7571819249846923</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8726278050195725</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.4580190361126076</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005561860264077447</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2506287708513495</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1860083510656061</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.01101381771178504</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1481053181946476</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.3099265673991937</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7623508321429403</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4980809296191196</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6736491520518402</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8990755888590045</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3645607261469849</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.4512387708036315</v>
+      </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1951800145897066</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.8574413833324961</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.6407895410572909</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.5264323490754701</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4468450886766275</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.7366073345631539</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.6943259403217087</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.8642905355121195</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.5719468136862718</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.5878517606815161</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.6197647065320203</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.1049580591073699</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1892,97 +2040,107 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06440917038609663</v>
+        <v>-0.02757852901484674</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.8542507163576309</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.7571819249846923</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.8726278050195725</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.4580190361126076</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.05664199358417291</v>
+        <v>0.005561860264077447</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.2506287708513495</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.1860083510656061</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.01101381771178504</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.1481053181946476</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>0.3099265673991937</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.7623508321429403</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0.4980809296191196</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0.6736491520518402</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.8990755888590045</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0.3645607261469849</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>-0.4512387708036315</v>
       </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.1951800145897066</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.8574413833324961</v>
+      </c>
       <c r="AA15" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.6407895410572909</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.5264323490754701</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.4468450886766275</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.7366073345631539</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.6943259403217087</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.8642905355121195</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.5719468136862718</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.5878517606815161</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6197647065320203</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.1049580591073699</v>
       </c>
     </row>
     <row r="16">
@@ -2019,19 +2177,37 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7378647873726218</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4</v>
+      </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>0.7745966692414833</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.9486832980505139</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.7745966692414833</v>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>1</v>
@@ -2076,97 +2252,107 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.03153571635729599</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.6910184067105104</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.7382166498895558</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.75782853486202</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.2305649712811109</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.05664199358417291</v>
+        <v>0.04984873366356304</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.1503606267718496</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5976143046671968</v>
+        <v>-0.07966649663613579</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.03760109012815547</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2279211529192759</v>
+        <v>-0.07780025828151069</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>-0.1298852140589887</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7623508321429403</v>
+      </c>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+        <v>0.7623508321429403</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3162277660168379</v>
+      </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0.7870728070034804</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.805211928902431</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0.7277811844324164</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>-0.0831509779424536</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>-0.5798728752256133</v>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.1648875440653483</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3119251469460218</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.8404886071070661</v>
+      </c>
       <c r="AA17" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.3713370446602164</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.5013853302863954</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.1934348484992942</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.5320925607891478</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.4956705675968203</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.745441055010835</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.6030417280456348</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.6921908206054923</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6409123710476698</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.3528238997118487</v>
       </c>
     </row>
     <row r="18">
@@ -2176,97 +2362,107 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.02165989122105998</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.5353784650110955</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.6993819380518612</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.6134903817115854</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.09114528105726209</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.1270453105501432</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.2054597298378407</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5976143046671968</v>
+        <v>-0.2167348679785508</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.1257372123861838</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2279211529192759</v>
+        <v>-0.3312642154769886</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>-0.2724606851434096</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4980809296191196</v>
+      </c>
       <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+        <v>0.4980809296191196</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.7870728070034804</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0.5659512365875284</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0.5954008071083364</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>-0.2800610017412986</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>-0.3180846537309496</v>
       </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>-0.2155727271443866</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.0490880693673816</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.8509099042394004</v>
+      </c>
       <c r="AA18" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.07077930784706449</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.3151717619646319</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.1605192517621251</v>
+        <v>-0.005773794280224241</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.2529993680396547</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.2328294022313889</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.424542777542034</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.4147867922191414</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.5762045823665686</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.4543333355777561</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.3641473782679506</v>
       </c>
     </row>
     <row r="19">
@@ -2276,97 +2472,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.0793980649914357</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.5391310127459359</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.590548807253591</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.611796914141652</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.08472991209930328</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.05664199358417291</v>
+        <v>0.1640220113992529</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.08108973939169131</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.223606797749979</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2182318387368158</v>
+        <v>0.04594375584248041</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.2090602720231013</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>-0.1115068113893674</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6736491520518402</v>
+      </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.6736491520518402</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.805211928902431</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0.5659512365875284</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0.6868295951599089</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0.1970059570589586</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>-0.5655209336910499</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.8404886071070661</v>
+      </c>
       <c r="AA19" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.2857983069734801</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.4794069199521</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.1675534711915676</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.4619111207686428</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.3273268353539885</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.6744882979413848</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.6034534106539285</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.5777562396116038</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6154244410706586</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.4113570019428818</v>
       </c>
     </row>
     <row r="20">
@@ -2376,97 +2576,107 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.03069077471302442</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.794300946050853</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.826454738200026</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.8563239866598242</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.2813198375645091</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.0255063758095474</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.2671924482255924</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.1256561724875087</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2182318387368158</v>
+        <v>0.02581816191170443</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.1091781663217261</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
+        <v>0.1646049004000574</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.8990755888590045</v>
+      </c>
       <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
+        <v>0.8990755888590045</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.7745966692414833</v>
+      </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0.7277811844324164</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0.5954008071083364</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0.6868295951599089</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0.2185862471932729</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>-0.5667350044327922</v>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>0.629940788348712</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.7745966692414833</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.8564759543080146</v>
+      </c>
       <c r="AA20" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.4100006994661819</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.503684648219569</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.214078807972236</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.5703341366581778</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.5348405573334052</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.7666594471413443</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.5934458298559258</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.734966380856178</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6147624402164161</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.2887675550020454</v>
       </c>
     </row>
     <row r="21">
@@ -2476,97 +2686,107 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06440917038609663</v>
+        <v>0.03214645210433645</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1101944348386703</v>
+        <v>0.1859161716969164</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03682187877349084</v>
+        <v>0.09782688783609415</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.08724386798967174</v>
+        <v>0.1768107388140629</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.1336565579070708</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.02746666031656214</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.1003925880219537</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5976143046671968</v>
+        <v>0.6623703042426295</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2182318387368158</v>
+        <v>0.01647412365930556</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2279211529192759</v>
+        <v>0.595077465684646</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
+        <v>0.3385714808706034</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3645607261469849</v>
+      </c>
       <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
+        <v>0.3645607261469849</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.9486832980505139</v>
+      </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>-0.0831509779424536</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>-0.2800610017412986</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.1970059570589586</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.2185862471932729</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>-0.06340542371062731</v>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>-0.8486684247915055</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.6324555320336759</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.3230702771333085</v>
+      </c>
       <c r="AA21" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.3378944486061889</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.1543033499620919</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.2926995929856517</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.3314109837539248</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1627913855112959</v>
+        <v>-0.03870624902856388</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.3873427457612049</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.2537817603626525</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.004171923996010908</v>
+        <v>-0.04323969948822864</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.125862896956603</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.0798948413381055</v>
       </c>
     </row>
     <row r="22">
@@ -2576,97 +2796,107 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06440917038609663</v>
+        <v>-0.1456855212497464</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1101944348386703</v>
+        <v>-0.2977193605035862</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.03682187877349084</v>
+        <v>-0.4526026019591243</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.08724386798967174</v>
+        <v>-0.4128148165287109</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1161095495804745</v>
+        <v>-0.1367417610658745</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.05664199358417291</v>
+        <v>-0.2058113265765833</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.05629849683222946</v>
+        <v>0.03047374490297631</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5976143046671968</v>
+        <v>-0.3115374735156035</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2182318387368158</v>
+        <v>-0.05321488691929668</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2279211529192759</v>
+        <v>-0.2696564558138487</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2390457218668787</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>0.2740219131903385</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.4512387708036315</v>
+      </c>
       <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
+        <v>-0.4512387708036315</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.7745966692414833</v>
+      </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>-0.5798728752256133</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>-0.3180846537309496</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>-0.5655209336910499</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>-0.5667350044327922</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>-0.06340542371062731</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>-0.629940788348712</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.7745966692414833</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.7755365347753621</v>
+      </c>
       <c r="AA22" t="n">
-        <v>-0.3350801813242426</v>
+        <v>-0.2013045687801563</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.1341862600304233</v>
+        <v>0.5138254785968848</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.02972030920988239</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.3239059431361432</v>
+        <v>-0.3441353582284666</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1627913855112959</v>
+        <v>-0.193390195754594</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.4101997847572218</v>
+        <v>0.5138288982293561</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.1613105200688691</v>
+        <v>-0.3928995060397543</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.004171923996010908</v>
+        <v>-0.5284827021480574</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.223771966253155</v>
+        <v>-0.5263060791369093</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0736986803191156</v>
+        <v>0.429438606795899</v>
       </c>
     </row>
     <row r="23">
@@ -2747,19 +2977,37 @@
       <c r="K24" t="n">
         <v>0.02825290943547103</v>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0.09194621406122841</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5030030300035687</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.2142857142857143</v>
+      </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>0.1648875440653483</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.2155727271443866</v>
+      </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>0.629940788348712</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.8486684247915055</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.629940788348712</v>
+      </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>1</v>
@@ -2835,19 +3083,37 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.0490880693673816</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.1951800145897066</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1951800145897066</v>
+      </c>
       <c r="P25" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>0.3119251469460218</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-0.0490880693673816</v>
+      </c>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>0.7745966692414833</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.6324555320336759</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.7745966692414833</v>
+      </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>0.7319250547113999</v>
@@ -2923,17 +3189,37 @@
       <c r="K26" t="n">
         <v>-0.1233730577518941</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0.1360120905009796</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.3059252255649718</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.8574413833324961</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8574413833324961</v>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>0.8404886071070661</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.8509099042394004</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.8404886071070661</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.8564759543080146</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.3230702771333085</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.7755365347753621</v>
+      </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -3005,32 +3291,38 @@
       <c r="K27" t="n">
         <v>-0.3601208505537725</v>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>-0.08143720110537678</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.4306884410120977</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.6407895410572909</v>
+      </c>
       <c r="O27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.6407895410572909</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.3713370446602164</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.07077930784706449</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.2857983069734801</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.4100006994661819</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>0.3378944486061889</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3350801813242426</v>
+        <v>-0.2013045687801563</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
@@ -3109,30 +3401,36 @@
       <c r="K28" t="n">
         <v>-0.2427695162366597</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>-0.2600731374244867</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1975926700229838</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.5264323490754701</v>
+      </c>
       <c r="O28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.5264323490754701</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.5013853302863954</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.3151717619646319</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.4794069199521</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.503684648219569</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>-0.1543033499620919</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.1341862600304233</v>
+        <v>0.5138254785968848</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
@@ -3211,32 +3509,38 @@
       <c r="K29" t="n">
         <v>-0.2893630806800999</v>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>-0.1847397329184985</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.504510918892574</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.4468450886766275</v>
+      </c>
       <c r="O29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.4468450886766275</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.1934348484992942</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>-0.005773794280224241</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.1675534711915676</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.214078807972236</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.2926995929856517</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1605192517621251</v>
+        <v>0.02972030920988239</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
@@ -3315,32 +3619,38 @@
       <c r="K30" t="n">
         <v>-0.3763809367128613</v>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0.008032162300804285</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3311701420320236</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.7366073345631539</v>
+      </c>
       <c r="O30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.7366073345631539</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.5320925607891478</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.2529993680396547</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.4619111207686428</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.5703341366581778</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>0.3314109837539248</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.3239059431361432</v>
+        <v>-0.3441353582284666</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
@@ -3419,32 +3729,38 @@
       <c r="K31" t="n">
         <v>-0.3002001735712182</v>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>-0.07980272769832711</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4970370832912829</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.6943259403217087</v>
+      </c>
       <c r="O31" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.6943259403217087</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.4956705675968203</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.2328294022313889</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.3273268353539885</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1627913855112959</v>
+        <v>0.5348405573334052</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1627913855112959</v>
+        <v>-0.03870624902856388</v>
       </c>
       <c r="V31" t="n">
-        <v>0.1627913855112959</v>
+        <v>-0.193390195754594</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
@@ -3521,32 +3837,38 @@
       <c r="K32" t="n">
         <v>0.3548151719441107</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0.1584649790632748</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.2747742542411711</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.8642905355121195</v>
+      </c>
       <c r="O32" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.8642905355121195</v>
       </c>
       <c r="P32" t="n">
         <v>-1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.745441055010835</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.424542777542034</v>
       </c>
       <c r="S32" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.6744882979413848</v>
       </c>
       <c r="T32" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.7666594471413443</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4101997847572218</v>
+        <v>-0.3873427457612049</v>
       </c>
       <c r="V32" t="n">
-        <v>0.4101997847572218</v>
+        <v>0.5138288982293561</v>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
@@ -3625,32 +3947,38 @@
       <c r="K33" t="n">
         <v>-0.1594257329488684</v>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0.08192901177024151</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.008082177995465454</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.5719468136862718</v>
+      </c>
       <c r="O33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.5719468136862718</v>
       </c>
       <c r="P33" t="n">
         <v>0.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.6030417280456348</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.4147867922191414</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.6034534106539285</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.5934458298559258</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>0.2537817603626525</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.1613105200688691</v>
+        <v>-0.3928995060397543</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
@@ -3729,32 +4057,38 @@
       <c r="K34" t="n">
         <v>-0.1788440266816468</v>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>-0.165142301603474</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.003704420553899844</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.5878517606815161</v>
+      </c>
       <c r="O34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.5878517606815161</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.6921908206054923</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.5762045823665686</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.5777562396116038</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>0.734966380856178</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>-0.04323969948822864</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.004171923996010908</v>
+        <v>-0.5284827021480574</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
@@ -3833,32 +4167,38 @@
       <c r="K35" t="n">
         <v>-0.1481655384303627</v>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0.008859623899229174</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.237519506159561</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.6197647065320203</v>
+      </c>
       <c r="O35" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6197647065320203</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6409123710476698</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.4543333355777561</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6154244410706586</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.6147624402164161</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.223771966253155</v>
+        <v>0.125862896956603</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.223771966253155</v>
+        <v>-0.5263060791369093</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
@@ -3937,32 +4277,38 @@
       <c r="K36" t="n">
         <v>-0.1266540164681085</v>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>-0.2960616827146957</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.3600966517658488</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.1049580591073699</v>
+      </c>
       <c r="O36" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.1049580591073699</v>
       </c>
       <c r="P36" t="n">
         <v>0.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.3528238997118487</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.3641473782679506</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.4113570019428818</v>
       </c>
       <c r="T36" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.2887675550020454</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0736986803191156</v>
+        <v>-0.0798948413381055</v>
       </c>
       <c r="V36" t="n">
-        <v>0.0736986803191156</v>
+        <v>0.429438606795899</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
